--- a/crawler/list.xlsx
+++ b/crawler/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheri\OneDrive\桌面\welfare\crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493AD8F1-7EFC-48CA-BAA8-000CB5232342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DEB106-0537-470E-B37B-0C50CC2403F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>url</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -46,15 +46,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新北2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>./NewTaipei/main1.py</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>./NewTaipei/main2.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -62,7 +54,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +76,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -102,15 +102,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -410,19 +413,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.4">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/crawler/list.xlsx
+++ b/crawler/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheri\OneDrive\桌面\welfare\crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DEB106-0537-470E-B37B-0C50CC2403F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFE2861-D532-40B9-B223-2EBD739EA8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.sw.ntpc.gov.tw/home.jsp?id=5afc03e40d8c7154</t>
-  </si>
-  <si>
     <t>city</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -42,11 +39,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新北1</t>
+    <t>新竹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>./NewTaipei/main1.py</t>
+    <t>https://social.hsinchu.gov.tw/cl.aspx?n=202</t>
+  </si>
+  <si>
+    <t>./Hsinchu/main1.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -106,10 +106,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -391,35 +394,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" ht="15.4">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.4">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/crawler/list.xlsx
+++ b/crawler/list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheri\OneDrive\桌面\welfare\crawler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\welfare\crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFE2861-D532-40B9-B223-2EBD739EA8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0BF7F2-F38F-499B-A242-64270FFC329F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,14 +39,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新竹</t>
+    <t>https://social.chiayi.gov.tw/cl.aspx?n=3891</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://social.hsinchu.gov.tw/cl.aspx?n=202</t>
-  </si>
-  <si>
-    <t>./Hsinchu/main1.py</t>
+    <t>嘉義市</t>
+  </si>
+  <si>
+    <t>./ChiayiCity/main1.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -54,7 +54,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +84,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -106,13 +112,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -397,7 +404,7 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.4">
+    <row r="1" spans="1:3" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -408,12 +415,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" ht="46.8">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -421,6 +428,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{BC39A952-5BE7-4332-B4C9-62AD1BF0CDB5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/crawler/list.xlsx
+++ b/crawler/list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\welfare\crawler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\flutter\welfare\crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0BF7F2-F38F-499B-A242-64270FFC329F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A304F6-FE52-4359-86BC-330617EBDA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>url</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,14 +39,62 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://social.chiayi.gov.tw/cl.aspx?n=3891</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嘉義市</t>
-  </si>
-  <si>
-    <t>./ChiayiCity/main1.py</t>
+    <t>新北</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sw.ntpc.gov.tw/home.jsp?id=5afc03e40d8c7154</t>
+  </si>
+  <si>
+    <t>encoding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gbk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新竹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://social.hsinchu.gov.tw/cl.aspx?n=202</t>
+  </si>
+  <si>
+    <t>./Hsinchu/main1.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/NewTaipei/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>main1.py</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -54,7 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,8 +135,17 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -112,7 +169,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
@@ -120,6 +177,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -401,10 +459,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6">
+    <row r="1" spans="1:4" ht="15.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -414,23 +472,44 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" ht="46.8">
+    <row r="2" spans="1:4" ht="45">
       <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{BC39A952-5BE7-4332-B4C9-62AD1BF0CDB5}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{5903547A-EB52-46F5-BBC7-D60852523B23}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/crawler/list.xlsx
+++ b/crawler/list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\flutter\welfare\crawler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\welfare\crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A304F6-FE52-4359-86BC-330617EBDA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72014296-3C30-4D9C-9928-39A183F6B169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>url</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,62 +39,94 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新北</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.sw.ntpc.gov.tw/home.jsp?id=5afc03e40d8c7154</t>
-  </si>
-  <si>
     <t>encoding</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>gbk</t>
+    <t>utf-8</t>
+  </si>
+  <si>
+    <t>嘉義</t>
+  </si>
+  <si>
+    <t>https://social.chiayi.gov.tw/</t>
+  </si>
+  <si>
+    <t>./ChiayiCity/main1.py</t>
+  </si>
+  <si>
+    <t>新北</t>
+  </si>
+  <si>
+    <t>https://www.sw.ntpc.gov.tw/home.jsp?id=5afc03e40d8c7154</t>
+  </si>
+  <si>
+    <t>./NewTaipei/main1.py</t>
+  </si>
+  <si>
+    <t>基隆</t>
+  </si>
+  <si>
+    <t>https://www.klcg.gov.tw/tw/social/2748.html</t>
+  </si>
+  <si>
+    <t>./Keelung/main1.py</t>
+  </si>
+  <si>
+    <t>桃園</t>
+  </si>
+  <si>
+    <t>https://sab.tycg.gov.tw/cl.aspx?n=7313</t>
+  </si>
+  <si>
+    <t>./Taoyuan/main1.py</t>
+  </si>
+  <si>
+    <t>新竹</t>
+  </si>
+  <si>
+    <t>https://social.hsinchu.gov.tw/Default.aspx</t>
+  </si>
+  <si>
+    <t>./Hsinchu/main1.py</t>
+  </si>
+  <si>
+    <t>苗栗</t>
+  </si>
+  <si>
+    <t>https://www.miaoli.gov.tw/social_affairs/News.aspx?n=693&amp;sms=9613</t>
+  </si>
+  <si>
+    <t>./Miaoli/main1.py</t>
+  </si>
+  <si>
+    <t>台中</t>
+  </si>
+  <si>
+    <t>https://www.taichung.gov.tw/10038/welfareList</t>
+  </si>
+  <si>
+    <t>./Taichung/main1.py</t>
+  </si>
+  <si>
+    <t>雲林</t>
+  </si>
+  <si>
+    <t>https://welfare.yunlin.gov.tw/</t>
+  </si>
+  <si>
+    <t>./yunlin/main1.py</t>
+  </si>
+  <si>
+    <t>新竹市</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新竹</t>
+    <t>https://society.hccg.gov.tw/ch/home.jsp?id=73&amp;parentpath=0,2,12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://social.hsinchu.gov.tw/cl.aspx?n=202</t>
-  </si>
-  <si>
-    <t>./Hsinchu/main1.py</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/NewTaipei/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>main1.py</t>
-    </r>
+    <t>./HsinchuCity/main1.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -102,7 +134,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +165,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
@@ -140,12 +178,16 @@
       <charset val="136"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,7 +198,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -164,20 +206,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -459,10 +528,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.4">
+    <row r="1" spans="1:4" ht="16.2" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -473,43 +542,149 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="105.6" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="75.599999999999994" thickBot="1">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="75.599999999999994" thickBot="1">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="42.6" thickBot="1">
+      <c r="A5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="75.599999999999994" thickBot="1">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="45.6" thickBot="1">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="45">
-      <c r="A2" s="4" t="s">
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.4">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="120.6" thickBot="1">
+      <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="90.6" thickBot="1">
+      <c r="A9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="60.6" thickBot="1">
+      <c r="A10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{5903547A-EB52-46F5-BBC7-D60852523B23}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{6B24962D-C1B8-44B0-9509-4295523AA2BD}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{CFDFB958-243A-49E0-8B47-E58F0411D909}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{ED0148FF-C3B5-4D49-9C7B-CA929DC74940}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{30A9DC98-9460-427D-84F8-038F4EA4218E}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{2859D62F-D92A-412B-BA00-D5A9F6D348B8}"/>
+    <hyperlink ref="B8" r:id="rId6" xr:uid="{4394203B-4D2D-4AD8-B848-DFE9187B57CB}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{E7459AF6-48E6-47C8-A1B9-5B36B08710A5}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{922A8F90-AC1E-45C3-8ADA-56B6CF446655}"/>
+    <hyperlink ref="B5" r:id="rId9" xr:uid="{48DE2D12-7242-4395-B86B-EF5A978C00BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>